--- a/medical_surveys_questionnaires/035_endodontic_referral_form--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/035_endodontic_referral_form--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first name</t>
+          <t>Patient's first name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last name</t>
+          <t>Patient's last name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,53 +571,53 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>State</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>zip_code</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>Zip code</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>zip_code</t>
+          <t>primary_insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zip code</t>
+          <t>Primary insurance</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>primary_insurance</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>primary insurance</t>
+          <t>Medical condition</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,69 +676,69 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>date_of_referral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medical condition</t>
+          <t>Date of referral</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>endodontist_recommended</t>
+          <t>date_of_last_visit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>endodontist recommended</t>
+          <t>Date of last visit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>date_of_referral</t>
+          <t>reason_for_referral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>date of referral</t>
+          <t>Reason for referral</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date_of_last_visit</t>
+          <t>next_appointment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date of last visit</t>
+          <t>Next appointment</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,330 +768,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>reason_for_referral</t>
+          <t>patient_signature</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>reason for referral</t>
+          <t>Patient signature</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>next_appointment</t>
+          <t>doctor_signature</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>next appointment</t>
+          <t>Doctor signature</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>patient_signature</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>patient signature</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>doctor_signature</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>doctor signature</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>signature of the dentist</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>dentist_name</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>dentist name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>date_of_referral</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>date of referral</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>date_of_last_visit</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>date of last visit</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>reason_for_referral</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>reason for referral</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>next_appointment</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>next appointment</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>patient_signature</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>patient signature</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>doctor_signature</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>doctor signature</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>signature of the dentist</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>dentist_name</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>dentist name</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>date_of_referral</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>date of referral</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>date_of_last_visit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>date of last visit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1106,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1513,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>mn</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mo</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mt</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nh</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nj</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NM</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1331,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nm</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1348,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nv</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1365,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ny</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1382,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1399,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>oh</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1416,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1433,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1450,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>pa</t>
+          <t>ri</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RI</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1467,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ri</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RI</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1484,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1501,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1518,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1535,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1552,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ut</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1569,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>va</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1586,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>vt</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1603,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>wa</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1620,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>wi</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>wv</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WV</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1654,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>wy</t>
+          <t>dc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1671,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dc</t>
+          <t>pr</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>PR</t>
         </is>
       </c>
     </row>
@@ -1972,29 +1688,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pr</t>
+          <t>us</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>US</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>primary_insurance_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>blue_cross</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Blue Cross</t>
         </is>
       </c>
     </row>
@@ -2006,12 +1722,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>blue_cross</t>
+          <t>aetna</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Blue Cross</t>
+          <t>Aetna</t>
         </is>
       </c>
     </row>
@@ -2023,12 +1739,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>aetna</t>
+          <t>united</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Aetna</t>
+          <t>United</t>
         </is>
       </c>
     </row>
@@ -2040,12 +1756,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>united</t>
+          <t>cigna</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>United</t>
+          <t>Cigna</t>
         </is>
       </c>
     </row>
@@ -2057,63 +1773,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>cigna</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cigna</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>primary_insurance_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>others</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
           <t>Others</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>endodontist_recommended_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>endodontist_recommended_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>False</t>
         </is>
       </c>
     </row>
